--- a/countries/de/1995-1999.xlsx
+++ b/countries/de/1995-1999.xlsx
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>

--- a/countries/de/1995-1999.xlsx
+++ b/countries/de/1995-1999.xlsx
@@ -765,6 +765,11 @@
       <c r="O2" t="n">
         <v>1983</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_DE_ECDC_AIDS_ANNUAL</t>
@@ -782,7 +787,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -792,6 +802,11 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -857,7 +872,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -872,17 +887,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -901,14 +916,39 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2229</v>
+        <v>1983</v>
       </c>
       <c r="O3" t="n">
-        <v>2229</v>
+        <v>1983</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,6 +956,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -923,16 +1021,26 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -998,7 +1106,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1013,43 +1121,68 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>D005</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1996-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1996-01</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1706</v>
+        <v>12198</v>
       </c>
       <c r="O4" t="n">
-        <v>1706</v>
+        <v>12198</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+          <t>SER_DE_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1057,6 +1190,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN4" t="b">
+        <v>0</v>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1064,16 +1255,31 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1174,19 +1380,24 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1996-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1996-01</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1871</v>
+        <v>2229</v>
       </c>
       <c r="O5" t="n">
-        <v>1871</v>
+        <v>2229</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1205,7 +1416,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1215,6 +1431,11 @@
       </c>
       <c r="AT5" t="n">
         <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1280,7 +1501,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1295,17 +1516,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>D005</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1315,23 +1536,48 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1995-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1151</v>
+        <v>2229</v>
       </c>
       <c r="O6" t="n">
-        <v>1151</v>
+        <v>2229</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1339,6 +1585,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN6" t="b">
+        <v>1</v>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1346,16 +1650,26 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1436,17 +1750,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,23 +1770,28 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2070</v>
+        <v>1706</v>
       </c>
       <c r="O7" t="n">
-        <v>2070</v>
+        <v>1706</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1487,16 +1806,26 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT7" t="n">
         <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1562,7 +1891,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1597,30 +1926,113 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1003</v>
+        <v>1706</v>
       </c>
       <c r="O8" t="n">
-        <v>1003</v>
+        <v>1706</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN8" t="b">
+        <v>1</v>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1628,7 +2040,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1638,6 +2055,11 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1703,7 +2125,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1718,17 +2140,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1738,23 +2160,48 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>51</v>
+        <v>11814</v>
       </c>
       <c r="O9" t="n">
-        <v>51</v>
+        <v>11814</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_DE_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1762,6 +2209,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>0</v>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1769,16 +2274,31 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1879,19 +2399,24 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1924</v>
+        <v>1871</v>
       </c>
       <c r="O10" t="n">
-        <v>1924</v>
+        <v>1871</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1910,7 +2435,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -1920,6 +2450,11 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -1985,7 +2520,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2000,17 +2535,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>D005</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2020,23 +2555,48 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1996-01-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>952</v>
+        <v>1871</v>
       </c>
       <c r="O11" t="n">
-        <v>952</v>
+        <v>1871</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2044,6 +2604,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2051,16 +2669,26 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
         </is>
       </c>
       <c r="AT11" t="n">
         <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2141,43 +2769,48 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>39</v>
+        <v>1151</v>
       </c>
       <c r="O12" t="n">
-        <v>39</v>
+        <v>1151</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2192,16 +2825,26 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT12" t="n">
         <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2267,7 +2910,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2282,17 +2925,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2302,23 +2945,48 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1746</v>
+        <v>1151</v>
       </c>
       <c r="O13" t="n">
-        <v>1746</v>
+        <v>1151</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2326,6 +2994,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2333,17 +3059,27 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -2380,6 +3116,4429 @@
         </is>
       </c>
       <c r="BC13" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1997-01-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1997-01</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>11163</v>
+      </c>
+      <c r="O14" t="n">
+        <v>11163</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1997-01-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1997-01</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2070</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2070</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1997-01-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1997-01</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>2070</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2070</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1003</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1003</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1003</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1003</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>10440</v>
+      </c>
+      <c r="O19" t="n">
+        <v>10440</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>51</v>
+      </c>
+      <c r="O21" t="n">
+        <v>51</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>51</v>
+      </c>
+      <c r="O22" t="n">
+        <v>51</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Invasive Haemophilus influenzae disease</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1924</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1924</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>1924</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1924</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>952</v>
+      </c>
+      <c r="O25" t="n">
+        <v>952</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>952</v>
+      </c>
+      <c r="O26" t="n">
+        <v>952</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_MEAS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_MEAS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>HOLD_DE_d87c84f420acb8e947e835322f96</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>9974</v>
+      </c>
+      <c r="O28" t="n">
+        <v>9974</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_TUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>HOLD_DE_1b0737fcd510170ff45815c0d362</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_PERT_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>HOLD_DE_b7116f22f4c269b49252863c2b1b</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>39</v>
+      </c>
+      <c r="O30" t="n">
+        <v>39</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>39</v>
+      </c>
+      <c r="O31" t="n">
+        <v>39</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Invasive Haemophilus influenzae disease</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>402</v>
+      </c>
+      <c r="O32" t="n">
+        <v>402</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_MENI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Invasive meningococcal disease</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>HOLD_DE_e9bcf1404b2e1bd6b7512d0fe790</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>1746</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1746</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1746</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1746</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
@@ -2511,7 +7670,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -2531,7 +7690,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -2541,7 +7700,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
